--- a/AtchisonRegime/Outputs/China/df_regCLI_China.xlsx
+++ b/AtchisonRegime/Outputs/China/df_regCLI_China.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H361"/>
+  <dimension ref="A1:H362"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9555,22 +9555,22 @@
         <v>45443</v>
       </c>
       <c r="B351" t="n">
-        <v>99.25</v>
+        <v>99.11408</v>
       </c>
       <c r="C351" t="n">
-        <v>99.58025333333335</v>
+        <v>99.53494666666667</v>
       </c>
       <c r="D351" t="n">
-        <v>99.66603722222223</v>
+        <v>99.66226166666667</v>
       </c>
       <c r="E351" t="n">
-        <v>1.128056363846663</v>
+        <v>1.129714846851707</v>
       </c>
       <c r="F351" t="b">
         <v>0</v>
       </c>
       <c r="G351" t="n">
-        <v>-0.2748089633951488</v>
+        <v>-0.3947190755637957</v>
       </c>
       <c r="H351" t="b">
         <v>0</v>
@@ -9581,22 +9581,22 @@
         <v>45473</v>
       </c>
       <c r="B352" t="n">
-        <v>99</v>
+        <v>98.87691</v>
       </c>
       <c r="C352" t="n">
-        <v>99.27</v>
+        <v>99.18366333333331</v>
       </c>
       <c r="D352" t="n">
-        <v>99.60172333333334</v>
+        <v>99.59452861111112</v>
       </c>
       <c r="E352" t="n">
-        <v>1.096911541228382</v>
+        <v>1.100493774051726</v>
       </c>
       <c r="F352" t="b">
         <v>0</v>
       </c>
       <c r="G352" t="n">
-        <v>-0.2279126352522796</v>
+        <v>-0.2155123505395301</v>
       </c>
       <c r="H352" t="b">
         <v>0</v>
@@ -9607,22 +9607,22 @@
         <v>45504</v>
       </c>
       <c r="B353" t="n">
-        <v>98.83</v>
+        <v>98.72803</v>
       </c>
       <c r="C353" t="n">
-        <v>99.02666666666666</v>
+        <v>98.90634</v>
       </c>
       <c r="D353" t="n">
-        <v>99.54463722222222</v>
+        <v>99.53461</v>
       </c>
       <c r="E353" t="n">
-        <v>1.081582254880357</v>
+        <v>1.086856881499526</v>
       </c>
       <c r="F353" t="b">
         <v>0</v>
       </c>
       <c r="G353" t="n">
-        <v>-0.1571771349177754</v>
+        <v>-0.1369821570201432</v>
       </c>
       <c r="H353" t="b">
         <v>0</v>
@@ -9633,22 +9633,22 @@
         <v>45535</v>
       </c>
       <c r="B354" t="n">
-        <v>98.77</v>
+        <v>98.69521</v>
       </c>
       <c r="C354" t="n">
-        <v>98.86666666666666</v>
+        <v>98.76671666666665</v>
       </c>
       <c r="D354" t="n">
-        <v>99.49789277777778</v>
+        <v>99.48578805555556</v>
       </c>
       <c r="E354" t="n">
-        <v>1.077567999001488</v>
+        <v>1.083904797516358</v>
       </c>
       <c r="F354" t="b">
         <v>0</v>
       </c>
       <c r="G354" t="n">
-        <v>-0.05568094083677352</v>
+        <v>-0.03027941206202257</v>
       </c>
       <c r="H354" t="b">
         <v>0</v>
@@ -9659,22 +9659,22 @@
         <v>45565</v>
       </c>
       <c r="B355" t="n">
-        <v>98.84</v>
+        <v>98.79619</v>
       </c>
       <c r="C355" t="n">
-        <v>98.81333333333333</v>
+        <v>98.73980999999999</v>
       </c>
       <c r="D355" t="n">
-        <v>99.4641038888889</v>
+        <v>99.45078222222223</v>
       </c>
       <c r="E355" t="n">
-        <v>1.078625309255862</v>
+        <v>1.085298762535294</v>
       </c>
       <c r="F355" t="b">
         <v>1</v>
       </c>
       <c r="G355" t="n">
-        <v>0.06489742026200002</v>
+        <v>0.09304350422744435</v>
       </c>
       <c r="H355" t="b">
         <v>0</v>
@@ -9685,22 +9685,22 @@
         <v>45596</v>
       </c>
       <c r="B356" t="n">
-        <v>99.03</v>
+        <v>99.0194</v>
       </c>
       <c r="C356" t="n">
-        <v>98.88</v>
+        <v>98.83693333333333</v>
       </c>
       <c r="D356" t="n">
-        <v>99.44494722222223</v>
+        <v>99.43133111111112</v>
       </c>
       <c r="E356" t="n">
-        <v>1.080080364741732</v>
+        <v>1.086616699531896</v>
       </c>
       <c r="F356" t="b">
         <v>1</v>
       </c>
       <c r="G356" t="n">
-        <v>0.1759128359355281</v>
+        <v>0.2054174209692945</v>
       </c>
       <c r="H356" t="b">
         <v>0</v>
@@ -9711,22 +9711,22 @@
         <v>45626</v>
       </c>
       <c r="B357" t="n">
-        <v>99.28</v>
+        <v>99.31903</v>
       </c>
       <c r="C357" t="n">
-        <v>99.05000000000001</v>
+        <v>99.04487333333333</v>
       </c>
       <c r="D357" t="n">
-        <v>99.44044611111111</v>
+        <v>99.42791416666665</v>
       </c>
       <c r="E357" t="n">
-        <v>1.080430411253582</v>
+        <v>1.086775457823675</v>
       </c>
       <c r="F357" t="b">
         <v>1</v>
       </c>
       <c r="G357" t="n">
-        <v>0.2313892661628568</v>
+        <v>0.2757055266963961</v>
       </c>
       <c r="H357" t="b">
         <v>1</v>
@@ -9737,22 +9737,22 @@
         <v>45657</v>
       </c>
       <c r="B358" t="n">
-        <v>99.58</v>
+        <v>99.65845</v>
       </c>
       <c r="C358" t="n">
-        <v>99.29666666666667</v>
+        <v>99.33229333333334</v>
       </c>
       <c r="D358" t="n">
-        <v>99.45090555555556</v>
+        <v>99.44055277777778</v>
       </c>
       <c r="E358" t="n">
-        <v>1.079893117019178</v>
+        <v>1.086736240917499</v>
       </c>
       <c r="F358" t="b">
         <v>1</v>
       </c>
       <c r="G358" t="n">
-        <v>0.277805270977266</v>
+        <v>0.3123296962227394</v>
       </c>
       <c r="H358" t="b">
         <v>1</v>
@@ -9763,22 +9763,22 @@
         <v>45688</v>
       </c>
       <c r="B359" t="n">
-        <v>99.88</v>
+        <v>100.0091</v>
       </c>
       <c r="C359" t="n">
-        <v>99.58</v>
+        <v>99.66219333333333</v>
       </c>
       <c r="D359" t="n">
-        <v>99.47590111111111</v>
+        <v>99.46913444444445</v>
       </c>
       <c r="E359" t="n">
-        <v>1.079099475223348</v>
+        <v>1.087812006083629</v>
       </c>
       <c r="F359" t="b">
         <v>1</v>
       </c>
       <c r="G359" t="n">
-        <v>0.2780095875200979</v>
+        <v>0.3223443003377225</v>
       </c>
       <c r="H359" t="b">
         <v>1</v>
@@ -9789,22 +9789,22 @@
         <v>45716</v>
       </c>
       <c r="B360" t="n">
-        <v>100.18</v>
+        <v>100.3596</v>
       </c>
       <c r="C360" t="n">
-        <v>99.88</v>
+        <v>100.00905</v>
       </c>
       <c r="D360" t="n">
-        <v>99.51541833333334</v>
+        <v>99.51364055555557</v>
       </c>
       <c r="E360" t="n">
-        <v>1.078083131932391</v>
+        <v>1.090632183059627</v>
       </c>
       <c r="F360" t="b">
         <v>1</v>
       </c>
       <c r="G360" t="n">
-        <v>0.2782716760091419</v>
+        <v>0.3213732415420884</v>
       </c>
       <c r="H360" t="b">
         <v>1</v>
@@ -9815,24 +9815,50 @@
         <v>45747</v>
       </c>
       <c r="B361" t="n">
-        <v>100.49</v>
+        <v>100.6996</v>
       </c>
       <c r="C361" t="n">
-        <v>100.1833333333333</v>
+        <v>100.3561</v>
       </c>
       <c r="D361" t="n">
-        <v>99.56963833333333</v>
+        <v>99.57368277777778</v>
       </c>
       <c r="E361" t="n">
-        <v>1.076608424402441</v>
+        <v>1.094880926304941</v>
       </c>
       <c r="F361" t="b">
         <v>1</v>
       </c>
       <c r="G361" t="n">
-        <v>0.2879412727724567</v>
+        <v>0.3105360517581144</v>
       </c>
       <c r="H361" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="2" t="n">
+        <v>45777</v>
+      </c>
+      <c r="B362" t="n">
+        <v>101.026</v>
+      </c>
+      <c r="C362" t="n">
+        <v>100.6950666666667</v>
+      </c>
+      <c r="D362" t="n">
+        <v>99.64837611111111</v>
+      </c>
+      <c r="E362" t="n">
+        <v>1.09981610236902</v>
+      </c>
+      <c r="F362" t="b">
+        <v>1</v>
+      </c>
+      <c r="G362" t="n">
+        <v>0.2967768877878058</v>
+      </c>
+      <c r="H362" t="b">
         <v>1</v>
       </c>
     </row>
